--- a/summer_camps/011_junior_golf_program_registration_form--summer_camps.xlsx
+++ b/summer_camps/011_junior_golf_program_registration_form--summer_camps.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'epilepsy'}</t>
+          <t>epilepsy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Epilepsy'}</t>
+          <t>Epilepsy</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'hypothyroidism'}</t>
+          <t>hypothyroidism</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Hypothyroidism'}</t>
+          <t>Hypothyroidism</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'food_allergy'}</t>
+          <t>food_allergy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Food Allergy'}</t>
+          <t>Food Allergy</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'latex_allergy'}</t>
+          <t>latex_allergy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Latex Allergy'}</t>
+          <t>Latex Allergy</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'shellfish_allergy'}</t>
+          <t>shellfish_allergy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Shellfish Allergy'}</t>
+          <t>Shellfish Allergy</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'brother'}</t>
+          <t>brother</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Brother'}</t>
+          <t>Brother</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'mother'}</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Mother'}</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'father'}</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Father'}</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'asian'}</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Asian'}</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'caucasian'}</t>
+          <t>caucasian</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Caucasian'}</t>
+          <t>Caucasian</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'african_american'}</t>
+          <t>african_american</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'African American'}</t>
+          <t>African American</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'american_indian/alaska_native'}</t>
+          <t>american_indian/alaska_native</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'American Indian/Alaska Native'}</t>
+          <t>American Indian/Alaska Native</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'asian'}</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Asian'}</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'hispanic_or_latino'}</t>
+          <t>hispanic_or_latino</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Hispanic or Latino'}</t>
+          <t>Hispanic or Latino</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'right-handed'}</t>
+          <t>right-handed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Right-Handed'}</t>
+          <t>Right-Handed</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'left-handed'}</t>
+          <t>left-handed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Left-Handed'}</t>
+          <t>Left-Handed</t>
         </is>
       </c>
     </row>
